--- a/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
@@ -85,13 +85,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASANOVA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>LUCIA</t>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
   </si>
 </sst>
 </file>
@@ -661,16 +661,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>43.33</v>
+      </c>
+      <c r="H2">
+        <v>5.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -684,16 +687,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>48.28</v>
+      </c>
+      <c r="H3">
+        <v>5.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -707,16 +713,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>60.87</v>
+      </c>
+      <c r="H4">
+        <v>5.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -730,16 +739,19 @@
         <v>12</v>
       </c>
       <c r="D5">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>58.33</v>
+      </c>
+      <c r="H5">
+        <v>5.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -753,16 +765,19 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -818,13 +833,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>43.33</v>
       </c>
       <c r="H2">
         <v>5.5</v>
@@ -853,7 +868,7 @@
         <v>48.28</v>
       </c>
       <c r="H3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,13 +885,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>65.22</v>
+        <v>60.87</v>
       </c>
       <c r="H4">
         <v>5.7</v>
@@ -905,7 +920,7 @@
         <v>58.33</v>
       </c>
       <c r="H5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -922,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -973,7 +988,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920347</v>
+        <v>22330051920050</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -985,10 +1000,10 @@
         <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
   <si>
     <t>Mat</t>
   </si>
@@ -85,13 +85,124 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MONDRAGON</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
     <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>ANGEL ADRIAN</t>
+  </si>
+  <si>
+    <t>MIREILLE</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
   </si>
 </sst>
 </file>
@@ -833,16 +944,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>43.33</v>
+        <v>46.67</v>
       </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -859,16 +970,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3">
-        <v>48.28</v>
+        <v>44.83</v>
       </c>
       <c r="H3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -911,16 +1022,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>58.33</v>
+        <v>75</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -946,7 +1057,7 @@
         <v>86.67</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,16 +1099,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920050</v>
+        <v>23330051920192</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1007,6 +1118,305 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920329</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>23330051920203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>23330051920332</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>23330051920211</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920050</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>23330051920241</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920243</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>23330051920335</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920249</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920253</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>23330051920273</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>23330051920320</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920314</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,30 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>LAGUNA</t>
+  </si>
+  <si>
+    <t>LOBATO</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -106,12 +130,6 @@
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>LAGUNA</t>
-  </si>
-  <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
@@ -124,6 +142,33 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>AUTRAN</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
+  </si>
+  <si>
+    <t>NATH</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
@@ -142,30 +187,45 @@
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>NATH</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
     <t>MONDRAGON</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>AXEL AARON</t>
+  </si>
+  <si>
+    <t>NATANAHEL</t>
+  </si>
+  <si>
+    <t>SERGIO EDUARDO</t>
+  </si>
+  <si>
+    <t>MIRIAM</t>
+  </si>
+  <si>
+    <t>AARON ZACHARY</t>
+  </si>
+  <si>
+    <t>DIANA LAURA</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
     <t>KEVYN DANIEL</t>
   </si>
   <si>
@@ -185,12 +245,6 @@
   </si>
   <si>
     <t>MARYSOL</t>
-  </si>
-  <si>
-    <t>AARON ZACHARY</t>
-  </si>
-  <si>
-    <t>DIANA LAURA</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
@@ -1067,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1099,16 +1153,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920192</v>
+        <v>23330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1122,16 +1176,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920329</v>
+        <v>23330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1145,16 +1199,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920203</v>
+        <v>23330051920208</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1168,22 +1222,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920332</v>
+        <v>23330051920233</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1191,22 +1245,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920211</v>
+        <v>23330051920243</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1214,22 +1268,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920050</v>
+        <v>23330051920335</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1237,16 +1291,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920241</v>
+        <v>23330051920264</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1260,16 +1314,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920243</v>
+        <v>23330051920267</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1283,22 +1337,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920335</v>
+        <v>23330051920365</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1306,116 +1360,277 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920249</v>
+        <v>23330051920192</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920253</v>
+        <v>23330051920329</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920273</v>
+        <v>23330051920203</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920320</v>
+        <v>23330051920332</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920314</v>
+        <v>23330051920211</v>
       </c>
       <c r="B15" t="s">
         <v>34</v>
       </c>
       <c r="C15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920050</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>23330051920241</v>
+      </c>
+      <c r="B17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D17" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>23330051920249</v>
+      </c>
+      <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>23330051920253</v>
+      </c>
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>23330051920273</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>23330051920320</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>19330051920314</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" t="s">
         <v>10</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F22" t="s">
         <v>15</v>
       </c>
-      <c r="G15">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
+++ b/docentes/Rodríguez Román Leticia - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="86">
   <si>
     <t>Mat</t>
   </si>
@@ -91,45 +91,51 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>GILES</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>SAN JUAN</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
     <t>LAGUNA</t>
   </si>
   <si>
     <t>LOBATO</t>
   </si>
   <si>
-    <t>SAN JUAN</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
@@ -151,42 +157,48 @@
     <t>VIVANCO</t>
   </si>
   <si>
+    <t>FIGUEROA</t>
+  </si>
+  <si>
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>NATH</t>
   </si>
   <si>
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>VERA</t>
   </si>
   <si>
@@ -208,43 +220,49 @@
     <t>SERGIO EDUARDO</t>
   </si>
   <si>
+    <t>ALEXA YAMILET</t>
+  </si>
+  <si>
     <t>MIRIAM</t>
   </si>
   <si>
+    <t>FERNANDA YAMILET</t>
+  </si>
+  <si>
+    <t>KARINA MONSERRATH</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>ABRAHAN</t>
+  </si>
+  <si>
+    <t>KEVYN DANIEL</t>
+  </si>
+  <si>
+    <t>SABDY</t>
+  </si>
+  <si>
+    <t>LUIS FABIAN</t>
+  </si>
+  <si>
+    <t>SERGIO JOSUE</t>
+  </si>
+  <si>
+    <t>DIEGO ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL CHARBEL</t>
+  </si>
+  <si>
+    <t>MARYSOL</t>
+  </si>
+  <si>
     <t>AARON ZACHARY</t>
   </si>
   <si>
     <t>DIANA LAURA</t>
-  </si>
-  <si>
-    <t>KARINA MONSERRATH</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>ABRAHAN</t>
-  </si>
-  <si>
-    <t>KEVYN DANIEL</t>
-  </si>
-  <si>
-    <t>SABDY</t>
-  </si>
-  <si>
-    <t>LUIS FABIAN</t>
-  </si>
-  <si>
-    <t>SERGIO JOSUE</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>MARYSOL</t>
   </si>
   <si>
     <t>ANGEL ADRIAN</t>
@@ -1121,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1159,10 +1177,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1182,10 +1200,10 @@
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1205,10 +1223,10 @@
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1222,16 +1240,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920233</v>
+        <v>23330051920231</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1245,16 +1263,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920243</v>
+        <v>23330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -1268,16 +1286,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920335</v>
+        <v>23330051920271</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1297,10 +1315,10 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1320,10 +1338,10 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1343,10 +1361,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1366,10 +1384,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1389,10 +1407,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1412,10 +1430,10 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1435,10 +1453,10 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1458,10 +1476,10 @@
         <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1481,10 +1499,10 @@
         <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1504,10 +1522,10 @@
         <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1521,16 +1539,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920249</v>
+        <v>23330051920243</v>
       </c>
       <c r="B18" t="s">
         <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
         <v>9</v>
@@ -1544,16 +1562,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920253</v>
+        <v>23330051920335</v>
       </c>
       <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1567,16 +1585,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920273</v>
+        <v>23330051920249</v>
       </c>
       <c r="B20" t="s">
         <v>39</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>9</v>
@@ -1590,22 +1608,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920320</v>
+        <v>23330051920253</v>
       </c>
       <c r="B21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -1613,24 +1631,70 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
+        <v>23330051920273</v>
+      </c>
+      <c r="B22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920320</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>19330051920314</v>
       </c>
-      <c r="B22" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="B24" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
         <v>10</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F24" t="s">
         <v>15</v>
       </c>
-      <c r="G22">
+      <c r="G24">
         <v>1</v>
       </c>
     </row>
